--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -869,57 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126375119</v>
+        <v>126375125</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>82789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484510</v>
+        <v>484574</v>
       </c>
       <c r="R4" t="n">
-        <v>6951281</v>
+        <v>6951299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,45 +966,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375125</v>
+        <v>126375119</v>
       </c>
       <c r="B5" t="n">
-        <v>82789</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484574</v>
+        <v>484510</v>
       </c>
       <c r="R5" t="n">
-        <v>6951299</v>
+        <v>6951281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,6 +1057,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126375122</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126375123</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126375125</v>
       </c>
       <c r="B4" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126375119</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>126375121</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>126375110</v>
       </c>
       <c r="B7" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>126375120</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -869,45 +869,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126375125</v>
+        <v>126375119</v>
       </c>
       <c r="B4" t="n">
-        <v>82792</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484574</v>
+        <v>484510</v>
       </c>
       <c r="R4" t="n">
-        <v>6951299</v>
+        <v>6951281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +960,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,57 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375119</v>
+        <v>126375125</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>82792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484510</v>
+        <v>484574</v>
       </c>
       <c r="R5" t="n">
-        <v>6951281</v>
+        <v>6951299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -869,57 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126375119</v>
+        <v>126375125</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>82792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484510</v>
+        <v>484574</v>
       </c>
       <c r="R4" t="n">
-        <v>6951281</v>
+        <v>6951299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,45 +966,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375125</v>
+        <v>126375119</v>
       </c>
       <c r="B5" t="n">
-        <v>82792</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484574</v>
+        <v>484510</v>
       </c>
       <c r="R5" t="n">
-        <v>6951299</v>
+        <v>6951281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,6 +1057,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -1076,32 +1076,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126375121</v>
+        <v>126375110</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484500</v>
+        <v>484606</v>
       </c>
       <c r="R6" t="n">
-        <v>6951264</v>
+        <v>6951273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,32 +1173,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126375110</v>
+        <v>126375121</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484606</v>
+        <v>484500</v>
       </c>
       <c r="R7" t="n">
-        <v>6951273</v>
+        <v>6951264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126375122</v>
+        <v>126375125</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484458</v>
+        <v>484574</v>
       </c>
       <c r="R2" t="n">
-        <v>6951365</v>
+        <v>6951299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126375123</v>
+        <v>126375121</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484542</v>
+        <v>484500</v>
       </c>
       <c r="R3" t="n">
-        <v>6951305</v>
+        <v>6951264</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126375125</v>
+        <v>126375122</v>
       </c>
       <c r="B4" t="n">
-        <v>82792</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484574</v>
+        <v>484458</v>
       </c>
       <c r="R4" t="n">
-        <v>6951299</v>
+        <v>6951365</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126375119</v>
+        <v>126375123</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,46 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484510</v>
+        <v>484542</v>
       </c>
       <c r="R5" t="n">
-        <v>6951281</v>
+        <v>6951305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1079,7 +1066,7 @@
         <v>126375110</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>80460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,45 +1160,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126375121</v>
+        <v>126375119</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484500</v>
+        <v>484510</v>
       </c>
       <c r="R7" t="n">
-        <v>6951264</v>
+        <v>6951281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,6 +1251,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>126375120</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31715-2025 artfynd.xlsx
+++ b/artfynd/A 31715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375122</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375123</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375119</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,8 +1412,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126375120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>